--- a/hira_material_automation/output/monthly/202601_202609__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:54:12</t>
+          <t>2026-09-14T23:45:45</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7ad0830234fea681785c54d2052eaf570b0d6e696e4f3b645bbd0b3c9f5c4a73</t>
+          <t>8929bc09495df53604bd6729a67827113d7748e932b254ace06e0723070f02ca</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:45</t>
+          <t>2026-09-24T23:49:09</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8929bc09495df53604bd6729a67827113d7748e932b254ace06e0723070f02ca</t>
+          <t>64eb047b354aeabde277d7f681d071ca59e6700f3a0a3ea5650e76da5c6407f3</t>
         </is>
       </c>
     </row>
